--- a/redemption/documentação/Fibonacci.xlsx
+++ b/redemption/documentação/Fibonacci.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{06239C61-7C45-470C-9C79-B1BEB025451A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rodri\Projeto-individual\redemption\documentação\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1150B3B6-8FC4-4AC2-BDA7-34EE09A3065D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -31,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="24">
-  <si>
-    <t>Requisitos</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="47">
   <si>
     <t>Descrição</t>
   </si>
@@ -103,13 +105,85 @@
   </si>
   <si>
     <t>Desenvolver o modelo de dados dentro da regra de negócio</t>
+  </si>
+  <si>
+    <t>Estilização do jodo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estilizar o jogo </t>
+  </si>
+  <si>
+    <t>Criação da dashbord</t>
+  </si>
+  <si>
+    <t>Estilização da dashbord</t>
+  </si>
+  <si>
+    <t>Criação de KPI's</t>
+  </si>
+  <si>
+    <t>Estilização das KPI's</t>
+  </si>
+  <si>
+    <t>Sessão da ODS</t>
+  </si>
+  <si>
+    <t>GG</t>
+  </si>
+  <si>
+    <t>Estilizar dashbord</t>
+  </si>
+  <si>
+    <t>Criar dashbord para visualização de dados</t>
+  </si>
+  <si>
+    <t>Criar KPI's para leitura de informações</t>
+  </si>
+  <si>
+    <t>Tema de ODS envolvendo o projeto</t>
+  </si>
+  <si>
+    <t>Estilização da sessão ODS</t>
+  </si>
+  <si>
+    <t>Estilizar sessão da ODS</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>Sprint2</t>
+  </si>
+  <si>
+    <t>Pontos Fibonacci</t>
+  </si>
+  <si>
+    <t>Planejado</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>SP1</t>
+  </si>
+  <si>
+    <t>SP2</t>
+  </si>
+  <si>
+    <t>Requisito</t>
+  </si>
+  <si>
+    <t>Entregue</t>
+  </si>
+  <si>
+    <t>Pendente</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -118,7 +192,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -131,8 +205,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -165,15 +251,48 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -186,224 +305,24 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left"/>
-      <border>
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical style="thin">
-          <color rgb="FF000000"/>
-        </vertical>
-        <horizontal style="thin">
-          <color rgb="FF000000"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left"/>
-      <border>
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical style="thin">
-          <color rgb="FF000000"/>
-        </vertical>
-        <horizontal style="thin">
-          <color rgb="FF000000"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left"/>
-      <border>
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical style="thin">
-          <color rgb="FF000000"/>
-        </vertical>
-        <horizontal style="thin">
-          <color rgb="FF000000"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left"/>
-      <border>
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical style="thin">
-          <color rgb="FF000000"/>
-        </vertical>
-        <horizontal style="thin">
-          <color rgb="FF000000"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left"/>
-      <border>
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical style="thin">
-          <color rgb="FF000000"/>
-        </vertical>
-        <horizontal style="thin">
-          <color rgb="FF000000"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical style="thin">
-          <color rgb="FF000000"/>
-        </vertical>
-        <horizontal style="thin">
-          <color rgb="FF000000"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left"/>
-      <border>
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical style="thin">
-          <color rgb="FF000000"/>
-        </vertical>
-        <horizontal style="thin">
-          <color rgb="FF000000"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left"/>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -416,20 +335,989 @@
 </styleSheet>
 </file>
 
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1E4B23D1-0DDD-4A71-BC40-BE77EF82DC05}" name="Tabela1" displayName="Tabela1" ref="C2:I8" totalsRowShown="0" dataDxfId="7">
-  <autoFilter ref="C2:I8" xr:uid="{1E4B23D1-0DDD-4A71-BC40-BE77EF82DC05}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{83EE354C-925A-43AB-98F1-8976CB0A61D6}" name="Requisitos" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{6F89703F-FB70-4215-82EE-8D5B8629BE09}" name="Descrição" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{8BD6802D-4DA2-4EA1-AEB2-09E15A609413}" name="Classificação" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{D7DBC0CE-8BCB-4849-9A6C-E038B145F2DC}" name="Tamanho" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{FDF231FC-2710-43A9-8B92-99AC482890E7}" name="Fibonacci" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{7C419DB5-56AD-4CE4-88F4-10F86DD49C07}" name="Prioridade" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{FAFEF2E8-E1EC-48E7-B13B-17B3428C6106}" name="Sprint" dataDxfId="0"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Planilha1!$M$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Planejado</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Planilha1!$K$3:$K$5</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>SP1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>SP2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Planilha1!$M$3:$M$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>59</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E73C-4D7C-9040-E3A623E87BCD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Planilha1!$N$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Entregue</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Planilha1!$K$3:$K$5</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>SP1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>SP2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Planilha1!$N$3:$N$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>38</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-E73C-4D7C-9040-E3A623E87BCD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1201234655"/>
+        <c:axId val="1201235135"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1201234655"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1201235135"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1201235135"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1201234655"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>4762</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>52387</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="12" name="Gráfico 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5F14729-4A9E-9849-E667-56C0179BEAFB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -749,182 +1637,415 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C2:I8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A2:O15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.42578125" customWidth="1"/>
     <col min="4" max="4" width="74.5703125" customWidth="1"/>
     <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.140625" customWidth="1"/>
+    <col min="13" max="13" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:9" ht="13.5" customHeight="1">
-      <c r="C2" t="s">
+    <row r="2" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="I2" t="s">
+      <c r="L2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C3" s="6" t="s">
         <v>6</v>
       </c>
+      <c r="D3" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="6">
+        <v>5</v>
+      </c>
+      <c r="H3" s="6">
+        <v>1</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="L3" s="1">
+        <f>SUM(G3:G15)</f>
+        <v>100</v>
+      </c>
+      <c r="M3" s="1">
+        <v>100</v>
+      </c>
+      <c r="N3" s="1">
+        <v>100</v>
+      </c>
+      <c r="O3" s="1">
+        <v>21</v>
+      </c>
     </row>
-    <row r="3" spans="3:9" ht="18.75" customHeight="1">
-      <c r="C3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="2" t="s">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="C4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="2">
+        <v>8</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="L4" s="1">
+        <f>SUM(G3:G9)</f>
+        <v>46</v>
+      </c>
+      <c r="M4" s="1">
+        <v>41</v>
+      </c>
+      <c r="N4" s="1">
+        <v>41</v>
+      </c>
+      <c r="O4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="2">
+        <v>13</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="L5" s="1">
+        <f>SUM(G10:G15)</f>
+        <v>54</v>
+      </c>
+      <c r="M5" s="1">
+        <v>59</v>
+      </c>
+      <c r="N5" s="1">
+        <v>38</v>
+      </c>
+      <c r="O5" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G6" s="2">
+        <v>5</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="1">
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="2">
         <v>5</v>
       </c>
-      <c r="H3" s="1">
+      <c r="H7" s="2">
         <v>1</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>11</v>
+      <c r="I7" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="4" spans="3:9">
-      <c r="C4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="4" t="s">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" s="2">
+        <v>5</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="2">
+        <v>5</v>
+      </c>
+      <c r="H9" s="2">
+        <v>2</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M9" s="1"/>
+      <c r="O9" s="1"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" s="2">
+        <v>21</v>
+      </c>
+      <c r="H10" s="2">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M10" s="1"/>
+      <c r="O10" s="1"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="2">
+        <v>5</v>
+      </c>
+      <c r="H11" s="2">
+        <v>2</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M11" s="1"/>
+      <c r="O11" s="1"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="2">
         <v>13</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="H12" s="2">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="3">
+      <c r="G13" s="2">
+        <v>5</v>
+      </c>
+      <c r="H13" s="2">
+        <v>1</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="3">
+      <c r="F14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G14" s="2">
+        <v>5</v>
+      </c>
+      <c r="H14" s="2">
         <v>1</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>11</v>
+      <c r="I14" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="5" spans="3:9">
-      <c r="C5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="3">
-        <v>13</v>
-      </c>
-      <c r="H5" s="3">
-        <v>1</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="3:9">
-      <c r="C6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C15" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" s="4">
         <v>5</v>
       </c>
-      <c r="H6" s="3">
-        <v>1</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="3:9">
-      <c r="C7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="3">
-        <v>5</v>
-      </c>
-      <c r="H7" s="3">
-        <v>1</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="3:9">
-      <c r="C8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="3">
-        <v>5</v>
-      </c>
-      <c r="H8" s="3">
-        <v>1</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>11</v>
+      <c r="H15" s="4">
+        <v>2</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/redemption/documentação/Fibonacci.xlsx
+++ b/redemption/documentação/Fibonacci.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rodri\Projeto-individual\redemption\documentação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1150B3B6-8FC4-4AC2-BDA7-34EE09A3065D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30F46C54-A59E-4D03-ABF4-64EC67AB858E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -350,6 +350,36 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR"/>
+              <a:t>Gráfico</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="pt-BR" baseline="0"/>
+              <a:t> de Burndown</a:t>
+            </a:r>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1283,16 +1313,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>609599</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>4762</xdr:rowOff>
+      <xdr:rowOff>4761</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>52387</xdr:rowOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>523875</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>133349</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
